--- a/ns-3.45/result_csv/cu_0116.xlsx
+++ b/ns-3.45/result_csv/cu_0116.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamikawa/Desktop/ns-allinone-3.45/ns-3.45/result_csv/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D768D7A2-EBAB-2046-B7B8-C4127541C508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC99EFAF-F3D7-0245-B479-C8D2CC8BC09E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38760" yWindow="780" windowWidth="38400" windowHeight="19200" xr2:uid="{0FB3E098-5F16-214F-9664-6534BF060B2E}"/>
   </bookViews>
@@ -1008,20 +1008,838 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ja-JP"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ja-JP"/>
+              <a:t>Utilization</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ja-JP" altLang="en-US"/>
+              <a:t>と再送率</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ja-JP"/>
+              <a:t>(100Mbps</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ja-JP" altLang="en-US"/>
+              <a:t>の場合</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ja-JP"/>
+              <a:t>)(%)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="38100">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$S$47:$S$60</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>-51.626199999999997</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-60.6571</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-63.564399999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-65.939800000000005</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-67.9482</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-69.688000000000002</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-71.2226</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-72.595299999999995</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-73.837100000000007</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-74.970699999999994</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-76.013599999999997</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-76.979100000000003</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-77.878</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-78.718900000000005</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$I$47:$I$60</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>82.169300000000007</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>82.139600000000002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>80.2761</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>84.754599999999996</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>82.311599999999999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>81.555199999999999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>82.298100000000005</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>88.567999999999998</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>88.650700000000001</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>86.559399999999997</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>82.664100000000005</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>90.934100000000001</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>89.580200000000005</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>77.300200000000004</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-07F3-D443-8FE4-89DDAE5887CA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="25400">
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$S$17:$S$30</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>-51.626199999999997</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-60.6571</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-63.564399999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-65.939800000000005</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-67.9482</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-69.688000000000002</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-71.2226</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-72.595299999999995</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-73.837100000000007</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-74.970699999999994</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-76.013599999999997</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-76.979100000000003</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-77.878</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-78.718900000000005</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$I$17:$I$30</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>79.579300000000003</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>79.479399999999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>79.820700000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>84.570300000000003</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>82.284000000000006</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>81.415300000000002</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>81.840299999999999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>88.686099999999996</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>88.620500000000007</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>86.566500000000005</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>82.894000000000005</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>90.485399999999998</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>89.585599999999999</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>77.080399999999997</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-07F3-D443-8FE4-89DDAE5887CA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="2"/>
+          <c:spPr>
+            <a:ln w="38100">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="9"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$S$32:$S$45</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>-51.626199999999997</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-60.6571</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-63.564399999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-65.939800000000005</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-67.9482</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-69.688000000000002</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-71.2226</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-72.595299999999995</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-73.837100000000007</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-74.970699999999994</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-76.013599999999997</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-76.979100000000003</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-77.878</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-78.718900000000005</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$I$32:$I$45</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>81.839200000000005</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>82.066299999999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>83.172300000000007</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>84.628200000000007</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>82.320099999999996</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>81.507400000000004</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>81.693200000000004</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>88.656499999999994</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>88.6417</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>86.563400000000001</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>90.061300000000003</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>90.895300000000006</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>89.507599999999996</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>77.020499999999998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-07F3-D443-8FE4-89DDAE5887CA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="3"/>
+          <c:spPr>
+            <a:ln w="38100">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$S$2:$S$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>-51.626199999999997</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-60.6571</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-63.564399999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-65.939800000000005</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-67.9482</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-69.688000000000002</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-71.2226</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-72.595299999999995</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-73.837100000000007</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-74.970699999999994</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-76.013599999999997</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-76.979100000000003</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-77.878</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-78.718900000000005</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$I$2:$I$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>58.722900000000003</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>58.710299999999997</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>61.257599999999996</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>66.320599999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>66.594700000000003</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>71.468900000000005</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>77.714500000000001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>85.357399999999998</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>85.418199999999999</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>85.6815</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>89.764499999999998</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>90.720699999999994</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>89.640600000000006</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>77.017899999999997</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-07F3-D443-8FE4-89DDAE5887CA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1568345152"/>
+        <c:axId val="1605481600"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1568345152"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ja-JP" altLang="en-US"/>
+                  <a:t>再送率</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1605481600"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1605481600"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="50"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ja-JP" altLang="en-US"/>
+                  <a:t>チャネル使用率</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1568345152"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ja-JP"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst/>
+  </c:chart>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ja-JP"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>403634</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>96130</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>529375</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>8110</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>479833</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>38980</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>605574</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>202445</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1041,6 +1859,44 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>402375</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>12574</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>478574</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>206909</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="グラフ 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0ED08E88-A16D-5046-B6E7-2D792D41352B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>

--- a/ns-3.45/result_csv/cu_0116.xlsx
+++ b/ns-3.45/result_csv/cu_0116.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamikawa/Desktop/ns-allinone-3.45/ns-3.45/result_csv/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamikawamasahiro/Desktop/ns-allinone-3.45/ns-3.45/result_csv/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC99EFAF-F3D7-0245-B479-C8D2CC8BC09E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EB2DEE6-220B-9948-950D-CA3ECCB28E22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38760" yWindow="780" windowWidth="38400" windowHeight="19200" xr2:uid="{0FB3E098-5F16-214F-9664-6534BF060B2E}"/>
+    <workbookView xWindow="20" yWindow="600" windowWidth="28800" windowHeight="16180" xr2:uid="{0FB3E098-5F16-214F-9664-6534BF060B2E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -176,1733 +176,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="ja-JP"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" altLang="ja-JP"/>
-              <a:t>Utilization</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="ja-JP" altLang="en-US"/>
-              <a:t>と再送率</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" altLang="ja-JP"/>
-              <a:t>(100Mbps</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="ja-JP" altLang="en-US"/>
-              <a:t>の場合</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" altLang="ja-JP"/>
-              <a:t>)(%)</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:v>400Mbps</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="38100">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$P$47:$P$60</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
-                <c:pt idx="0">
-                  <c:v>16.741399999999999</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>16.415500000000002</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>18.575399999999998</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>16.933900000000001</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>18.924900000000001</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>23.1708</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>25.738099999999999</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>19.711200000000002</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>17.360299999999999</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>20.5214</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>51.796799999999998</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>19.0625</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>21.035</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>30.5853</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$I$47:$I$60</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
-                <c:pt idx="0">
-                  <c:v>82.169300000000007</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>82.139600000000002</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>80.2761</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>84.754599999999996</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>82.311599999999999</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>81.555199999999999</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>82.298100000000005</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>88.567999999999998</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>88.650700000000001</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>86.559399999999997</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>82.664100000000005</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>90.934100000000001</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>89.580200000000005</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>77.300200000000004</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000008-290E-B644-A6DD-A4E17910E326}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:v>200Mbps</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="25400">
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$P$17:$P$30</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
-                <c:pt idx="0">
-                  <c:v>14.313499999999999</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>15.204499999999999</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>20.590299999999999</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>16.9237</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>18.7196</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>22.262899999999998</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>26.859500000000001</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>19.255400000000002</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>17.928000000000001</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>20.928699999999999</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>46.786999999999999</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>20.878499999999999</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>20.389600000000002</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>32.936399999999999</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$I$17:$I$30</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
-                <c:pt idx="0">
-                  <c:v>79.579300000000003</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>79.479399999999998</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>79.820700000000002</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>84.570300000000003</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>82.284000000000006</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>81.415300000000002</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>81.840299999999999</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>88.686099999999996</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>88.620500000000007</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>86.566500000000005</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>82.894000000000005</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>90.485399999999998</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>89.585599999999999</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>77.080399999999997</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000009-290E-B644-A6DD-A4E17910E326}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:v>300Mbps</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="38100">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="9"/>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$P$32:$P$45</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
-                <c:pt idx="0">
-                  <c:v>16.127199999999998</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>16.431799999999999</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>23.571300000000001</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>17.0868</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>18.631699999999999</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>21.6111</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>26.790099999999999</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>18.7502</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>19.010300000000001</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>20.398900000000001</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>25.244800000000001</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>20.028700000000001</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>21.858799999999999</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>33.912999999999997</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$I$32:$I$45</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
-                <c:pt idx="0">
-                  <c:v>81.839200000000005</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>82.066299999999998</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>83.172300000000007</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>84.628200000000007</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>82.320099999999996</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>81.507400000000004</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>81.693200000000004</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>88.656499999999994</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>88.6417</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>86.563400000000001</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>90.061300000000003</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>90.895300000000006</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>89.507599999999996</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>77.020499999999998</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-290E-B644-A6DD-A4E17910E326}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:v>100Mbps</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="38100">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$P$2:$P$15</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
-                <c:pt idx="0">
-                  <c:v>13.83</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>13.688700000000001</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>16.950800000000001</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>16.214600000000001</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>17.6769</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>20.404199999999999</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>26.365500000000001</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>17.284800000000001</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>16.974499999999999</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>19.296700000000001</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>23.879799999999999</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>20.603899999999999</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>20.3416</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>34.289499999999997</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$I$2:$I$15</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
-                <c:pt idx="0">
-                  <c:v>58.722900000000003</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>58.710299999999997</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>61.257599999999996</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>66.320599999999999</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>66.594700000000003</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>71.468900000000005</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>77.714500000000001</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>85.357399999999998</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>85.418199999999999</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>85.6815</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>89.764499999999998</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>90.720699999999994</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>89.640600000000006</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>77.017899999999997</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000007-290E-B644-A6DD-A4E17910E326}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="1568345152"/>
-        <c:axId val="1605481600"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="1568345152"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="ja-JP" altLang="en-US"/>
-                  <a:t>再送率</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="ja-JP"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1605481600"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="1605481600"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-          <c:min val="50"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="ja-JP" altLang="en-US"/>
-                  <a:t>チャネル使用率</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="ja-JP"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1568345152"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="t"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="ja-JP"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst/>
-  </c:chart>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="ja-JP"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="ja-JP"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" altLang="ja-JP"/>
-              <a:t>Utilization</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="ja-JP" altLang="en-US"/>
-              <a:t>と再送率</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" altLang="ja-JP"/>
-              <a:t>(100Mbps</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="ja-JP" altLang="en-US"/>
-              <a:t>の場合</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" altLang="ja-JP"/>
-              <a:t>)(%)</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="0"/>
-          <c:spPr>
-            <a:ln w="38100">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$S$47:$S$60</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
-                <c:pt idx="0">
-                  <c:v>-51.626199999999997</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-60.6571</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>-63.564399999999999</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>-65.939800000000005</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>-67.9482</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>-69.688000000000002</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>-71.2226</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>-72.595299999999995</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>-73.837100000000007</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>-74.970699999999994</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>-76.013599999999997</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>-76.979100000000003</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>-77.878</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>-78.718900000000005</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$I$47:$I$60</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
-                <c:pt idx="0">
-                  <c:v>82.169300000000007</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>82.139600000000002</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>80.2761</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>84.754599999999996</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>82.311599999999999</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>81.555199999999999</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>82.298100000000005</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>88.567999999999998</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>88.650700000000001</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>86.559399999999997</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>82.664100000000005</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>90.934100000000001</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>89.580200000000005</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>77.300200000000004</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-07F3-D443-8FE4-89DDAE5887CA}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="1"/>
-          <c:spPr>
-            <a:ln w="25400">
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$S$17:$S$30</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
-                <c:pt idx="0">
-                  <c:v>-51.626199999999997</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-60.6571</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>-63.564399999999999</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>-65.939800000000005</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>-67.9482</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>-69.688000000000002</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>-71.2226</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>-72.595299999999995</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>-73.837100000000007</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>-74.970699999999994</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>-76.013599999999997</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>-76.979100000000003</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>-77.878</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>-78.718900000000005</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$I$17:$I$30</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
-                <c:pt idx="0">
-                  <c:v>79.579300000000003</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>79.479399999999998</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>79.820700000000002</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>84.570300000000003</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>82.284000000000006</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>81.415300000000002</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>81.840299999999999</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>88.686099999999996</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>88.620500000000007</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>86.566500000000005</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>82.894000000000005</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>90.485399999999998</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>89.585599999999999</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>77.080399999999997</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-07F3-D443-8FE4-89DDAE5887CA}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="2"/>
-          <c:spPr>
-            <a:ln w="38100">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="9"/>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$S$32:$S$45</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
-                <c:pt idx="0">
-                  <c:v>-51.626199999999997</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-60.6571</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>-63.564399999999999</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>-65.939800000000005</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>-67.9482</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>-69.688000000000002</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>-71.2226</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>-72.595299999999995</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>-73.837100000000007</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>-74.970699999999994</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>-76.013599999999997</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>-76.979100000000003</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>-77.878</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>-78.718900000000005</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$I$32:$I$45</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
-                <c:pt idx="0">
-                  <c:v>81.839200000000005</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>82.066299999999998</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>83.172300000000007</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>84.628200000000007</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>82.320099999999996</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>81.507400000000004</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>81.693200000000004</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>88.656499999999994</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>88.6417</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>86.563400000000001</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>90.061300000000003</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>90.895300000000006</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>89.507599999999996</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>77.020499999999998</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-07F3-D443-8FE4-89DDAE5887CA}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="3"/>
-          <c:spPr>
-            <a:ln w="38100">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$S$2:$S$15</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
-                <c:pt idx="0">
-                  <c:v>-51.626199999999997</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-60.6571</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>-63.564399999999999</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>-65.939800000000005</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>-67.9482</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>-69.688000000000002</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>-71.2226</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>-72.595299999999995</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>-73.837100000000007</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>-74.970699999999994</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>-76.013599999999997</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>-76.979100000000003</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>-77.878</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>-78.718900000000005</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$I$2:$I$15</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
-                <c:pt idx="0">
-                  <c:v>58.722900000000003</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>58.710299999999997</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>61.257599999999996</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>66.320599999999999</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>66.594700000000003</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>71.468900000000005</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>77.714500000000001</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>85.357399999999998</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>85.418199999999999</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>85.6815</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>89.764499999999998</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>90.720699999999994</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>89.640600000000006</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>77.017899999999997</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-07F3-D443-8FE4-89DDAE5887CA}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="1568345152"/>
-        <c:axId val="1605481600"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="1568345152"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="ja-JP" altLang="en-US"/>
-                  <a:t>再送率</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="ja-JP"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1605481600"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="1605481600"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-          <c:min val="50"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="ja-JP" altLang="en-US"/>
-                  <a:t>チャネル使用率</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="ja-JP"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1568345152"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="t"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="ja-JP"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst/>
-  </c:chart>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="ja-JP"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>529375</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>8110</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>605574</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>202445</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="グラフ 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63295C57-9E2F-A39E-7111-C22C485F1CA7}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>402375</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>12574</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>478574</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>206909</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="5" name="グラフ 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0ED08E88-A16D-5046-B6E7-2D792D41352B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5828,6 +4101,5 @@
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>